--- a/data/trans_camb/IP08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 12,21</t>
+          <t>-1,42; 12,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 6,66</t>
+          <t>-8,03; 6,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 36,13</t>
+          <t>-4,23; 37,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 8,77</t>
+          <t>-6,48; 10,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -1,07</t>
+          <t>-14,9; -1,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 15,81</t>
+          <t>-3,29; 17,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,32</t>
+          <t>-2,72; 8,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 0,48</t>
+          <t>-9,41; 0,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 21,79</t>
+          <t>-0,46; 20,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 254,7</t>
+          <t>-16,86; 251,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 124,72</t>
+          <t>-69,33; 128,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 659,91</t>
+          <t>-47,27; 872,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 106,1</t>
+          <t>-39,36; 129,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,86; -0,92</t>
+          <t>-91,88; -3,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 184,16</t>
+          <t>-22,4; 215,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 114,92</t>
+          <t>-20,87; 110,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 9,39</t>
+          <t>-73,53; 7,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 269,12</t>
+          <t>-9,59; 268,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,19</t>
+          <t>1,78; 8,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,99</t>
+          <t>-3,37; 2,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,98</t>
+          <t>-2,38; 3,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,26</t>
+          <t>-0,59; 6,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,23</t>
+          <t>-6,31; -0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 7,78</t>
+          <t>-2,07; 8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,19</t>
+          <t>1,35; 6,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,16</t>
+          <t>-4,21; -0,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,4</t>
+          <t>-1,32; 4,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 142,11</t>
+          <t>19,49; 144,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 33,42</t>
+          <t>-38,71; 36,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 70,63</t>
+          <t>-28,43; 64,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 67,59</t>
+          <t>-4,63; 65,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,12; -1,94</t>
+          <t>-49,38; -3,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 78,08</t>
+          <t>-17,15; 80,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 74,59</t>
+          <t>12,88; 74,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,73; -1,45</t>
+          <t>-40,2; -2,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 50,84</t>
+          <t>-13,85; 53,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 4,11</t>
+          <t>-6,14; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,96</t>
+          <t>-8,8; 1,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 7,09</t>
+          <t>-4,3; 7,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 4,82</t>
+          <t>-6,52; 4,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,19; -1,91</t>
+          <t>-11,99; -2,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 5,89</t>
+          <t>-6,4; 5,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,42</t>
+          <t>-4,39; 3,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -1,87</t>
+          <t>-8,98; -2,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,74</t>
+          <t>-3,78; 4,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 54,14</t>
+          <t>-49,01; 56,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 16,44</t>
+          <t>-64,54; 14,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 92,88</t>
+          <t>-35,29; 105,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 51,9</t>
+          <t>-41,74; 50,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,93; -16,1</t>
+          <t>-77,33; -24,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 62,43</t>
+          <t>-40,24; 63,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 39,58</t>
+          <t>-33,94; 33,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,59; -18,22</t>
+          <t>-65,63; -21,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 49,58</t>
+          <t>-29,52; 49,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,9</t>
+          <t>0,93; 6,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,7</t>
+          <t>-3,62; 0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,54</t>
+          <t>-1,4; 4,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,77</t>
+          <t>-0,77; 5,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,29</t>
+          <t>-6,74; -1,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 5,82</t>
+          <t>-1,42; 6,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,46</t>
+          <t>0,76; 4,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -1,57</t>
+          <t>-4,88; -1,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,15</t>
+          <t>-0,78; 4,49</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 84,63</t>
+          <t>9,58; 87,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 10,26</t>
+          <t>-39,5; 9,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 61,77</t>
+          <t>-16,04; 67,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 47,08</t>
+          <t>-6,72; 53,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,24; -21,18</t>
+          <t>-53,1; -19,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 56,24</t>
+          <t>-11,76; 57,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 48,2</t>
+          <t>7,21; 51,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,78; -16,25</t>
+          <t>-45,09; -16,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 44,51</t>
+          <t>-7,54; 47,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 12,6</t>
+          <t>-1,89; 13,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 6,4</t>
+          <t>-8,29; 6,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 37,3</t>
+          <t>-4,53; 34,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 10,2</t>
+          <t>-5,43; 10,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,9; -1,06</t>
+          <t>-14,98; -1,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 17,11</t>
+          <t>-3,83; 16,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,66</t>
+          <t>-2,57; 9,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 0,25</t>
+          <t>-9,78; 0,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 20,43</t>
+          <t>-0,22; 20,78</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 251,87</t>
+          <t>-20,41; 275,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 128,67</t>
+          <t>-70,41; 144,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 872,04</t>
+          <t>-50,15; 1123,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 129,51</t>
+          <t>-36,54; 147,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,88; -3,2</t>
+          <t>-91,04; -6,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 215,78</t>
+          <t>-25,69; 203,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 110,12</t>
+          <t>-22,95; 114,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 7,89</t>
+          <t>-74,31; 11,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 268,08</t>
+          <t>-5,1; 276,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,23</t>
+          <t>1,75; 8,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,28</t>
+          <t>-3,27; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,93</t>
+          <t>-1,87; 4,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 6,15</t>
+          <t>-0,15; 6,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -0,36</t>
+          <t>-6,14; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 8,26</t>
+          <t>-2,24; 7,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,18</t>
+          <t>1,66; 6,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -0,23</t>
+          <t>-4,38; -0,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,8</t>
+          <t>-1,34; 4,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,49; 144,03</t>
+          <t>17,79; 138,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,71; 36,36</t>
+          <t>-36,42; 37,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 64,3</t>
+          <t>-21,3; 74,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 65,77</t>
+          <t>-1,67; 71,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,38; -3,07</t>
+          <t>-48,13; -0,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 80,16</t>
+          <t>-19,22; 75,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 74,96</t>
+          <t>15,48; 78,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,2; -2,84</t>
+          <t>-40,62; -0,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 53,24</t>
+          <t>-13,1; 56,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 4,02</t>
+          <t>-5,79; 3,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 1,06</t>
+          <t>-8,51; 1,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 7,34</t>
+          <t>-4,2; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 4,99</t>
+          <t>-6,37; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -2,58</t>
+          <t>-12,49; -2,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 5,95</t>
+          <t>-6,26; 6,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 3,21</t>
+          <t>-5,14; 2,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; -2,05</t>
+          <t>-8,69; -1,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,67</t>
+          <t>-3,82; 4,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 56,49</t>
+          <t>-46,59; 51,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 14,68</t>
+          <t>-65,52; 16,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 105,62</t>
+          <t>-34,3; 87,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 50,56</t>
+          <t>-43,44; 58,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,33; -24,62</t>
+          <t>-77,59; -21,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 63,14</t>
+          <t>-40,79; 67,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 33,93</t>
+          <t>-36,62; 31,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,63; -21,28</t>
+          <t>-65,7; -15,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 49,88</t>
+          <t>-28,71; 47,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,05</t>
+          <t>0,9; 6,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,66</t>
+          <t>-3,91; 0,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,8</t>
+          <t>-1,17; 4,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,24</t>
+          <t>-0,66; 4,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -1,96</t>
+          <t>-7,09; -2,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,07</t>
+          <t>-1,75; 6,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,6</t>
+          <t>0,77; 4,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -1,49</t>
+          <t>-4,72; -1,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,49</t>
+          <t>-0,72; 4,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,58; 87,15</t>
+          <t>9,76; 87,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 9,05</t>
+          <t>-40,35; 14,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 67,2</t>
+          <t>-13,58; 67,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 53,43</t>
+          <t>-5,11; 48,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,1; -19,88</t>
+          <t>-55,03; -22,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 57,92</t>
+          <t>-13,73; 58,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 51,42</t>
+          <t>6,59; 50,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -16,51</t>
+          <t>-43,52; -14,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 47,16</t>
+          <t>-6,84; 45,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-7,9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,9</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>3,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 13,38</t>
+          <t>-7,26; 8,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 6,56</t>
+          <t>-15,3; -1,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 34,25</t>
+          <t>-4,37; 15,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 10,29</t>
+          <t>-2,07; 12,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -1,33</t>
+          <t>-8,29; 6,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 16,26</t>
+          <t>-6,76; 10,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 9,45</t>
+          <t>-2,3; 9,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 0,37</t>
+          <t>-9,67; 0,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 20,78</t>
+          <t>-2,91; 10,69</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-66,15%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>60,39%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-12,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-66,15%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 275,89</t>
+          <t>-44,05; 106,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 144,31</t>
+          <t>-91,86; -0,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 1123,88</t>
+          <t>-29,57; 184,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 147,56</t>
+          <t>-17,52; 254,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,04; -6,94</t>
+          <t>-69,8; 124,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 203,73</t>
+          <t>-62,36; 193,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 114,43</t>
+          <t>-18,26; 114,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 11,75</t>
+          <t>-75,33; 9,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 276,0</t>
+          <t>-23,98; 139,57</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,64</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,19</t>
+          <t>-0,34; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,15</t>
+          <t>-6,42; -0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,23</t>
+          <t>-2,72; 6,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 6,66</t>
+          <t>1,49; 8,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -0,13</t>
+          <t>-3,52; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 7,58</t>
+          <t>-1,67; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,6</t>
+          <t>1,55; 6,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,1</t>
+          <t>-4,15; -0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,88</t>
+          <t>-1,07; 4,23</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-29,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>65,25%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-8,66%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-29,42%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 138,31</t>
+          <t>-3,12; 67,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 37,37</t>
+          <t>-50,12; -1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 74,78</t>
+          <t>-22,28; 68,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 71,07</t>
+          <t>17,48; 142,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,13; -0,45</t>
+          <t>-39,64; 33,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 75,57</t>
+          <t>-19,51; 75,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 78,47</t>
+          <t>14,42; 74,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,62; -0,54</t>
+          <t>-39,73; -1,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 56,13</t>
+          <t>-10,84; 49,65</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,51</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,0</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,86</t>
+          <t>-6,68; 4,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 1,13</t>
+          <t>-12,19; -1,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 6,52</t>
+          <t>-6,82; 5,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,35</t>
+          <t>-6,05; 4,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -2,31</t>
+          <t>-8,42; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 6,26</t>
+          <t>-4,18; 7,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,87</t>
+          <t>-4,56; 3,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -1,51</t>
+          <t>-8,87; -1,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,44</t>
+          <t>-3,99; 4,78</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,43%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-56,28%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-5,58%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-10,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-34,23%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,43%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-56,28%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,2%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 51,54</t>
+          <t>-41,46; 51,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 16,6</t>
+          <t>-76,93; -16,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 87,49</t>
+          <t>-46,06; 58,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 58,45</t>
+          <t>-47,52; 54,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,59; -21,23</t>
+          <t>-62,8; 16,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 67,18</t>
+          <t>-33,25; 102,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 31,58</t>
+          <t>-34,98; 39,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,7; -15,53</t>
+          <t>-65,59; -18,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 47,19</t>
+          <t>-29,31; 50,19</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,64</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,03</t>
+          <t>-0,64; 4,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,94</t>
+          <t>-7,14; -2,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,82</t>
+          <t>-2,11; 5,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,94</t>
+          <t>0,79; 5,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -2,33</t>
+          <t>-3,9; 0,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,36</t>
+          <t>-1,38; 3,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,63</t>
+          <t>0,7; 4,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -1,47</t>
+          <t>-4,8; -1,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,38</t>
+          <t>-0,97; 3,65</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-40,07%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>41,2%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-17,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-40,07%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 87,89</t>
+          <t>-5,08; 47,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 14,23</t>
+          <t>-54,24; -21,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 67,58</t>
+          <t>-16,9; 50,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 48,75</t>
+          <t>7,67; 84,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -22,13</t>
+          <t>-40,67; 10,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 58,82</t>
+          <t>-15,27; 57,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 50,29</t>
+          <t>5,87; 48,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,52; -14,82</t>
+          <t>-43,78; -16,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 45,88</t>
+          <t>-9,72; 38,65</t>
         </is>
       </c>
     </row>
